--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/125.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/125.xlsx
@@ -426,13 +426,13 @@
         <v>-15.30356411727221</v>
       </c>
       <c r="E2">
-        <v>-9.16278505808158</v>
+        <v>-9.092426157424406</v>
       </c>
       <c r="F2">
-        <v>-3.791236456581965</v>
+        <v>-4.324550159280522</v>
       </c>
       <c r="G2">
-        <v>-5.242723420116374</v>
+        <v>-7.361350075064981</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.76043685509415</v>
       </c>
       <c r="E3">
-        <v>-8.101790768928462</v>
+        <v>-10.17627112642023</v>
       </c>
       <c r="F3">
-        <v>-3.790292117742773</v>
+        <v>-4.406609890936648</v>
       </c>
       <c r="G3">
-        <v>-5.178568358110838</v>
+        <v>-6.85324754569764</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.16052346406487</v>
       </c>
       <c r="E4">
-        <v>-10.81799664957319</v>
+        <v>-10.42519681414786</v>
       </c>
       <c r="F4">
-        <v>-4.115315322109604</v>
+        <v>-4.475812532133921</v>
       </c>
       <c r="G4">
-        <v>-4.518150939027168</v>
+        <v>-7.219807700533441</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.56249483854224</v>
       </c>
       <c r="E5">
-        <v>-10.24858632784872</v>
+        <v>-11.60673908138516</v>
       </c>
       <c r="F5">
-        <v>-3.4909698404152</v>
+        <v>-4.54070849120404</v>
       </c>
       <c r="G5">
-        <v>-4.170464204310751</v>
+        <v>-6.259504513774891</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.94461316319827</v>
       </c>
       <c r="E6">
-        <v>-10.12619526084341</v>
+        <v>-12.04542141545621</v>
       </c>
       <c r="F6">
-        <v>-4.181346144521558</v>
+        <v>-4.406633913591328</v>
       </c>
       <c r="G6">
-        <v>-3.844368847601461</v>
+        <v>-5.794710541152295</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.30404972728495</v>
       </c>
       <c r="E7">
-        <v>-12.76357399443662</v>
+        <v>-12.55554495547226</v>
       </c>
       <c r="F7">
-        <v>-4.378686454155678</v>
+        <v>-4.805354480683023</v>
       </c>
       <c r="G7">
-        <v>-3.181283128813138</v>
+        <v>-5.803291475190086</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.63488500432672</v>
       </c>
       <c r="E8">
-        <v>-12.65704164340617</v>
+        <v>-13.30916454288074</v>
       </c>
       <c r="F8">
-        <v>-4.410284528735466</v>
+        <v>-4.560460911923794</v>
       </c>
       <c r="G8">
-        <v>-3.004682077020717</v>
+        <v>-5.646202778806129</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.94267186028018</v>
       </c>
       <c r="E9">
-        <v>-12.36712873743512</v>
+        <v>-13.41650296228456</v>
       </c>
       <c r="F9">
-        <v>-4.463905579086081</v>
+        <v>-4.552866439574928</v>
       </c>
       <c r="G9">
-        <v>-3.553616875069429</v>
+        <v>-4.412511430869024</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.22422243352279</v>
       </c>
       <c r="E10">
-        <v>-13.26032947918203</v>
+        <v>-14.1983168288648</v>
       </c>
       <c r="F10">
-        <v>-4.281980358450657</v>
+        <v>-4.942326687470727</v>
       </c>
       <c r="G10">
-        <v>-3.002656023150683</v>
+        <v>-4.115300583989876</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.499871400027125</v>
       </c>
       <c r="E11">
-        <v>-14.03369321326396</v>
+        <v>-15.30194670080013</v>
       </c>
       <c r="F11">
-        <v>-4.419064394837738</v>
+        <v>-4.733236814595298</v>
       </c>
       <c r="G11">
-        <v>-2.17472831032543</v>
+        <v>-4.111973485722908</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.797623202251689</v>
       </c>
       <c r="E12">
-        <v>-16.96369740875882</v>
+        <v>-15.74646170939305</v>
       </c>
       <c r="F12">
-        <v>-4.415121366000412</v>
+        <v>-4.94679572960883</v>
       </c>
       <c r="G12">
-        <v>-0.8791529346227296</v>
+        <v>-3.603798124353702</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.146866494720713</v>
       </c>
       <c r="E13">
-        <v>-14.87321342412394</v>
+        <v>-16.51949033639841</v>
       </c>
       <c r="F13">
-        <v>-4.40022814846548</v>
+        <v>-4.937738360426621</v>
       </c>
       <c r="G13">
-        <v>-1.533320043728255</v>
+        <v>-2.976108758471267</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.590566418592269</v>
       </c>
       <c r="E14">
-        <v>-16.98292983786939</v>
+        <v>-17.00165507789111</v>
       </c>
       <c r="F14">
-        <v>-4.073737905428291</v>
+        <v>-4.634003369944334</v>
       </c>
       <c r="G14">
-        <v>-1.543211953799598</v>
+        <v>-2.261808900190419</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.173299668373766</v>
       </c>
       <c r="E15">
-        <v>-17.50411643988618</v>
+        <v>-17.98548416995352</v>
       </c>
       <c r="F15">
-        <v>-3.889098953181295</v>
+        <v>-4.411844344554938</v>
       </c>
       <c r="G15">
-        <v>-0.233728976286419</v>
+        <v>-2.298314285851963</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.930085269384115</v>
       </c>
       <c r="E16">
-        <v>-18.22023573403715</v>
+        <v>-19.35336861413245</v>
       </c>
       <c r="F16">
-        <v>-3.740646402558193</v>
+        <v>-4.299226139409539</v>
       </c>
       <c r="G16">
-        <v>0.3492150560872265</v>
+        <v>-1.590499786282547</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.894780452028715</v>
       </c>
       <c r="E17">
-        <v>-19.46212444590067</v>
+        <v>-19.88860254252104</v>
       </c>
       <c r="F17">
-        <v>-4.167267212143578</v>
+        <v>-3.8037928496736</v>
       </c>
       <c r="G17">
-        <v>1.107849740229994</v>
+        <v>-1.540017277354201</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.09000651349402</v>
       </c>
       <c r="E18">
-        <v>-20.24066422577336</v>
+        <v>-20.5353501433485</v>
       </c>
       <c r="F18">
-        <v>-3.462223834803251</v>
+        <v>-3.732168890557943</v>
       </c>
       <c r="G18">
-        <v>1.414330114619103</v>
+        <v>-1.47956340526157</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.512910160431395</v>
       </c>
       <c r="E19">
-        <v>-22.28963568917992</v>
+        <v>-21.5009838268481</v>
       </c>
       <c r="F19">
-        <v>-3.331558817420463</v>
+        <v>-3.618220327363649</v>
       </c>
       <c r="G19">
-        <v>0.9671018966278794</v>
+        <v>-1.411452241336604</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.140211935678323</v>
       </c>
       <c r="E20">
-        <v>-21.03506725009493</v>
+        <v>-21.89876045520786</v>
       </c>
       <c r="F20">
-        <v>-3.214615706065048</v>
+        <v>-3.169511100982615</v>
       </c>
       <c r="G20">
-        <v>0.6780879605039655</v>
+        <v>-1.91358585709664</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.932305008841261</v>
       </c>
       <c r="E21">
-        <v>-21.20987087526501</v>
+        <v>-22.6209479045291</v>
       </c>
       <c r="F21">
-        <v>-2.779508272437983</v>
+        <v>-3.081060514813892</v>
       </c>
       <c r="G21">
-        <v>0.94075326468082</v>
+        <v>-1.839101893008578</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.833300455234307</v>
       </c>
       <c r="E22">
-        <v>-23.71484155734795</v>
+        <v>-23.37800913218341</v>
       </c>
       <c r="F22">
-        <v>-2.353000120819379</v>
+        <v>-2.62703151297208</v>
       </c>
       <c r="G22">
-        <v>1.446869466724599</v>
+        <v>-1.723507574413846</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.77866109970444</v>
       </c>
       <c r="E23">
-        <v>-23.28463652661926</v>
+        <v>-22.97750183399704</v>
       </c>
       <c r="F23">
-        <v>-2.258976278764621</v>
+        <v>-2.304002188943788</v>
       </c>
       <c r="G23">
-        <v>0.9446928138725528</v>
+        <v>-2.122206505344893</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.70478761811834</v>
       </c>
       <c r="E24">
-        <v>-22.95259522695485</v>
+        <v>-23.99381819859048</v>
       </c>
       <c r="F24">
-        <v>-1.894811057880708</v>
+        <v>-2.510748610436697</v>
       </c>
       <c r="G24">
-        <v>0.04999470806573955</v>
+        <v>-1.698036237034693</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.55161495574466</v>
       </c>
       <c r="E25">
-        <v>-22.20057871934508</v>
+        <v>-23.2703718334951</v>
       </c>
       <c r="F25">
-        <v>-2.286763034924128</v>
+        <v>-2.275769771121575</v>
       </c>
       <c r="G25">
-        <v>0.1039466687192421</v>
+        <v>-1.686588370559894</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.26764000525485</v>
       </c>
       <c r="E26">
-        <v>-24.59702452183419</v>
+        <v>-23.43492752198582</v>
       </c>
       <c r="F26">
-        <v>-2.057902517246083</v>
+        <v>-2.109700330943136</v>
       </c>
       <c r="G26">
-        <v>0.2348390182509463</v>
+        <v>-1.807449767107606</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.82043816543732</v>
       </c>
       <c r="E27">
-        <v>-23.8516060008536</v>
+        <v>-23.84098672930561</v>
       </c>
       <c r="F27">
-        <v>-2.120860096593651</v>
+        <v>-2.181074123103147</v>
       </c>
       <c r="G27">
-        <v>-0.02329745962818526</v>
+        <v>-2.61706685255515</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.19864377796717</v>
       </c>
       <c r="E28">
-        <v>-23.22309003638101</v>
+        <v>-24.24808748564716</v>
       </c>
       <c r="F28">
-        <v>-1.973238398475557</v>
+        <v>-1.986793802654968</v>
       </c>
       <c r="G28">
-        <v>-0.05276131492769882</v>
+        <v>-2.930797321675263</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.40712576365421</v>
       </c>
       <c r="E29">
-        <v>-24.3258640267289</v>
+        <v>-23.43791178635688</v>
       </c>
       <c r="F29">
-        <v>-2.110405271602918</v>
+        <v>-2.466187414370501</v>
       </c>
       <c r="G29">
-        <v>-0.3013501794715723</v>
+        <v>-2.622545805422644</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.47123269748301</v>
       </c>
       <c r="E30">
-        <v>-23.30712945701536</v>
+        <v>-22.81562700211885</v>
       </c>
       <c r="F30">
-        <v>-2.063427727822756</v>
+        <v>-1.919301740144475</v>
       </c>
       <c r="G30">
-        <v>0.1110411678099002</v>
+        <v>-2.277785592962942</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.43128397059785</v>
       </c>
       <c r="E31">
-        <v>-22.98540402114042</v>
+        <v>-23.08790603030404</v>
       </c>
       <c r="F31">
-        <v>-1.985398831948654</v>
+        <v>-2.496460929473212</v>
       </c>
       <c r="G31">
-        <v>-0.5282053125501304</v>
+        <v>-2.654002609136799</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.32754633673516</v>
       </c>
       <c r="E32">
-        <v>-22.82775425551139</v>
+        <v>-23.08908796202004</v>
       </c>
       <c r="F32">
-        <v>-1.563174996537329</v>
+        <v>-2.100068074783384</v>
       </c>
       <c r="G32">
-        <v>0.4807165459981566</v>
+        <v>-2.332926039465043</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.19935247740374</v>
       </c>
       <c r="E33">
-        <v>-23.04930984633666</v>
+        <v>-22.01900049705952</v>
       </c>
       <c r="F33">
-        <v>-2.153832432694683</v>
+        <v>-2.217692932511302</v>
       </c>
       <c r="G33">
-        <v>0.2542950943852431</v>
+        <v>-2.431841829632927</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.07839842316562</v>
       </c>
       <c r="E34">
-        <v>-22.45250678533979</v>
+        <v>-21.74078463945028</v>
       </c>
       <c r="F34">
-        <v>-2.211201845542965</v>
+        <v>-2.494394981170629</v>
       </c>
       <c r="G34">
-        <v>-0.4152263249314225</v>
+        <v>-2.119250188178324</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.97752285113756</v>
       </c>
       <c r="E35">
-        <v>-22.39079274156326</v>
+        <v>-21.48519756645736</v>
       </c>
       <c r="F35">
-        <v>-1.998642769984612</v>
+        <v>-2.092955712262947</v>
       </c>
       <c r="G35">
-        <v>-0.03296094205731785</v>
+        <v>-2.110219019947192</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.89995639128644</v>
       </c>
       <c r="E36">
-        <v>-21.66553045839081</v>
+        <v>-21.55654820292222</v>
       </c>
       <c r="F36">
-        <v>-1.708610633079435</v>
+        <v>-2.358918805912381</v>
       </c>
       <c r="G36">
-        <v>0.1836579842138137</v>
+        <v>-2.041379536003587</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.83948955351133</v>
       </c>
       <c r="E37">
-        <v>-22.26443925980124</v>
+        <v>-21.12363061626294</v>
       </c>
       <c r="F37">
-        <v>-2.322805300619934</v>
+        <v>-2.361135517082273</v>
       </c>
       <c r="G37">
-        <v>0.989315657196389</v>
+        <v>-1.765511776216119</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.77632537234822</v>
       </c>
       <c r="E38">
-        <v>-20.26380019947855</v>
+        <v>-20.70563887993294</v>
       </c>
       <c r="F38">
-        <v>-1.837236209916531</v>
+        <v>-2.004129047293353</v>
       </c>
       <c r="G38">
-        <v>0.9398561068396776</v>
+        <v>-1.686724102927004</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.6905698861073</v>
       </c>
       <c r="E39">
-        <v>-20.02743197017419</v>
+        <v>-20.35092803938613</v>
       </c>
       <c r="F39">
-        <v>-1.548166635933407</v>
+        <v>-2.373639723027531</v>
       </c>
       <c r="G39">
-        <v>0.3727364821437483</v>
+        <v>-1.302369765817619</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.56410574763889</v>
       </c>
       <c r="E40">
-        <v>-19.45121082354218</v>
+        <v>-20.46598750697301</v>
       </c>
       <c r="F40">
-        <v>-1.82858391239429</v>
+        <v>-2.33953997889129</v>
       </c>
       <c r="G40">
-        <v>1.114513868400547</v>
+        <v>-0.9225012179139466</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.37678891138883</v>
       </c>
       <c r="E41">
-        <v>-19.18624528087938</v>
+        <v>-19.67618994071725</v>
       </c>
       <c r="F41">
-        <v>-1.995471779566696</v>
+        <v>-2.156830294325414</v>
       </c>
       <c r="G41">
-        <v>0.4384673638259777</v>
+        <v>-0.9121160365572528</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.12092024365605</v>
       </c>
       <c r="E42">
-        <v>-18.14635820907601</v>
+        <v>-19.46221954385483</v>
       </c>
       <c r="F42">
-        <v>-1.883147644849291</v>
+        <v>-2.270425973006116</v>
       </c>
       <c r="G42">
-        <v>1.189792363418034</v>
+        <v>-0.8436638864417425</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.80074307568916</v>
       </c>
       <c r="E43">
-        <v>-18.15830885198226</v>
+        <v>-18.27477667498553</v>
       </c>
       <c r="F43">
-        <v>-2.13091730523104</v>
+        <v>-2.53382361280908</v>
       </c>
       <c r="G43">
-        <v>1.068480732676981</v>
+        <v>-0.7459961719421639</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.4222664568655</v>
       </c>
       <c r="E44">
-        <v>-18.49618282616855</v>
+        <v>-18.59679646167097</v>
       </c>
       <c r="F44">
-        <v>-1.568163425036987</v>
+        <v>-2.53804000288933</v>
       </c>
       <c r="G44">
-        <v>0.8162899945863805</v>
+        <v>0.1138816158825949</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.00160791788743</v>
       </c>
       <c r="E45">
-        <v>-17.77140056124091</v>
+        <v>-17.21982789863265</v>
       </c>
       <c r="F45">
-        <v>-2.007815282235811</v>
+        <v>-2.140050884214307</v>
       </c>
       <c r="G45">
-        <v>0.8962760853607117</v>
+        <v>-0.8809869768514859</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.56014080996364</v>
       </c>
       <c r="E46">
-        <v>-17.52469835425104</v>
+        <v>-17.20370653116534</v>
       </c>
       <c r="F46">
-        <v>-2.035013069171927</v>
+        <v>-2.54537850971073</v>
       </c>
       <c r="G46">
-        <v>1.397999193473878</v>
+        <v>-0.3863385045557421</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.11317206074542</v>
       </c>
       <c r="E47">
-        <v>-17.09690247169444</v>
+        <v>-16.901227109823</v>
       </c>
       <c r="F47">
-        <v>-1.958552272791324</v>
+        <v>-2.597771091202994</v>
       </c>
       <c r="G47">
-        <v>1.442353882609033</v>
+        <v>-0.4831852037615815</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.68001710784361</v>
       </c>
       <c r="E48">
-        <v>-15.79209061349434</v>
+        <v>-15.83081359473393</v>
       </c>
       <c r="F48">
-        <v>-2.131501304250014</v>
+        <v>-2.503755532822264</v>
       </c>
       <c r="G48">
-        <v>0.6786871692465736</v>
+        <v>-0.857170912241969</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.27844173013922</v>
       </c>
       <c r="E49">
-        <v>-14.991918313287</v>
+        <v>-16.1404525334824</v>
       </c>
       <c r="F49">
-        <v>-2.440416904469408</v>
+        <v>-2.517522170689389</v>
       </c>
       <c r="G49">
-        <v>0.7600173415098489</v>
+        <v>-0.7652701680718008</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.914538993081617</v>
       </c>
       <c r="E50">
-        <v>-14.97360969287399</v>
+        <v>-15.37477814826549</v>
       </c>
       <c r="F50">
-        <v>-2.007358023429466</v>
+        <v>-2.436375299911149</v>
       </c>
       <c r="G50">
-        <v>1.147662360885269</v>
+        <v>-0.3903707490225745</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.597607133440899</v>
       </c>
       <c r="E51">
-        <v>-14.2505074918032</v>
+        <v>-15.01322478349309</v>
       </c>
       <c r="F51">
-        <v>-2.472633769499086</v>
+        <v>-2.634920884116343</v>
       </c>
       <c r="G51">
-        <v>1.239059902133468</v>
+        <v>-0.267801110976598</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.335920067968056</v>
       </c>
       <c r="E52">
-        <v>-14.36140982025104</v>
+        <v>-14.61669801395945</v>
       </c>
       <c r="F52">
-        <v>-2.144091660405163</v>
+        <v>-2.734587564918971</v>
       </c>
       <c r="G52">
-        <v>1.213562080390002</v>
+        <v>-0.7432384875079511</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.127180676627594</v>
       </c>
       <c r="E53">
-        <v>-14.22989840659429</v>
+        <v>-15.03067752231865</v>
       </c>
       <c r="F53">
-        <v>-2.40394223098934</v>
+        <v>-2.792166554720162</v>
       </c>
       <c r="G53">
-        <v>0.5831944831662962</v>
+        <v>-1.237443346701432</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.972250049751862</v>
       </c>
       <c r="E54">
-        <v>-14.09201995848275</v>
+        <v>-13.41727280286586</v>
       </c>
       <c r="F54">
-        <v>-2.340487631200093</v>
+        <v>-2.532323439442611</v>
       </c>
       <c r="G54">
-        <v>0.4702022533654313</v>
+        <v>-0.5181611173839815</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.870359071748874</v>
       </c>
       <c r="E55">
-        <v>-12.59955719435281</v>
+        <v>-13.3682928279989</v>
       </c>
       <c r="F55">
-        <v>-2.166518879468557</v>
+        <v>-2.629693885804678</v>
       </c>
       <c r="G55">
-        <v>0.03902024960305557</v>
+        <v>-1.172722181408681</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.81007574926636</v>
       </c>
       <c r="E56">
-        <v>-12.14429611693968</v>
+        <v>-12.6843302277764</v>
       </c>
       <c r="F56">
-        <v>-2.143867172839005</v>
+        <v>-2.628051233244927</v>
       </c>
       <c r="G56">
-        <v>0.2401921703879478</v>
+        <v>-1.312456998075778</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.784225659277576</v>
       </c>
       <c r="E57">
-        <v>-11.65501261430693</v>
+        <v>-12.5342565991622</v>
       </c>
       <c r="F57">
-        <v>-2.130321709068427</v>
+        <v>-2.749165174473437</v>
       </c>
       <c r="G57">
-        <v>0.2761149000345794</v>
+        <v>-0.9307047497602605</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.785012667561656</v>
       </c>
       <c r="E58">
-        <v>-12.22632489511462</v>
+        <v>-12.94696813479925</v>
       </c>
       <c r="F58">
-        <v>-2.085800274637565</v>
+        <v>-2.355292213422925</v>
       </c>
       <c r="G58">
-        <v>0.04129459438853487</v>
+        <v>-0.9796081284663746</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.796269431509717</v>
       </c>
       <c r="E59">
-        <v>-10.4667229207982</v>
+        <v>-12.48012774934852</v>
       </c>
       <c r="F59">
-        <v>-2.344688282299689</v>
+        <v>-2.834424889406576</v>
       </c>
       <c r="G59">
-        <v>-0.5151286576700091</v>
+        <v>-1.593479277267891</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.808134053663725</v>
       </c>
       <c r="E60">
-        <v>-9.132738633040688</v>
+        <v>-12.79567181820299</v>
       </c>
       <c r="F60">
-        <v>-1.968043706492601</v>
+        <v>-2.699837552371532</v>
       </c>
       <c r="G60">
-        <v>-0.9961409928894949</v>
+        <v>-1.370861642479601</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.813035997208502</v>
       </c>
       <c r="E61">
-        <v>-10.08577863032495</v>
+        <v>-11.92430737812106</v>
       </c>
       <c r="F61">
-        <v>-2.448900215041478</v>
+        <v>-2.663299922968851</v>
       </c>
       <c r="G61">
-        <v>-0.569474573242685</v>
+        <v>-1.474673729500066</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.798385321642526</v>
       </c>
       <c r="E62">
-        <v>-9.014504705174422</v>
+        <v>-11.88286731247687</v>
       </c>
       <c r="F62">
-        <v>-1.774125382599445</v>
+        <v>-2.740290046119843</v>
       </c>
       <c r="G62">
-        <v>-0.7994813456746293</v>
+        <v>-1.964972144957208</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.759392573791164</v>
       </c>
       <c r="E63">
-        <v>-9.849120578684101</v>
+        <v>-10.66859323511213</v>
       </c>
       <c r="F63">
-        <v>-2.491565278122666</v>
+        <v>-2.777904553146163</v>
       </c>
       <c r="G63">
-        <v>-0.4642852992778823</v>
+        <v>-2.173235254287219</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.694275752540541</v>
       </c>
       <c r="E64">
-        <v>-9.232808851662188</v>
+        <v>-10.98939939076351</v>
       </c>
       <c r="F64">
-        <v>-2.318362766238721</v>
+        <v>-2.543127007109922</v>
       </c>
       <c r="G64">
-        <v>-0.594316906969376</v>
+        <v>-2.666327770179505</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.596976458681725</v>
       </c>
       <c r="E65">
-        <v>-8.622393197798262</v>
+        <v>-10.9980125483261</v>
       </c>
       <c r="F65">
-        <v>-2.168984100859288</v>
+        <v>-2.853927143170685</v>
       </c>
       <c r="G65">
-        <v>-1.509331830750696</v>
+        <v>-2.110507037409108</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.467666891419899</v>
       </c>
       <c r="E66">
-        <v>-8.200796796158158</v>
+        <v>-10.46876979104967</v>
       </c>
       <c r="F66">
-        <v>-2.807687674746417</v>
+        <v>-2.835504252132424</v>
       </c>
       <c r="G66">
-        <v>-0.9845640151386634</v>
+        <v>-2.438754248718925</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.309184143367705</v>
       </c>
       <c r="E67">
-        <v>-8.107410605171982</v>
+        <v>-10.55338885635699</v>
       </c>
       <c r="F67">
-        <v>-2.237998702656126</v>
+        <v>-2.688346439759898</v>
       </c>
       <c r="G67">
-        <v>-1.271737287942743</v>
+        <v>-2.760029451123037</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.121491981219016</v>
       </c>
       <c r="E68">
-        <v>-8.916155306675838</v>
+        <v>-9.986306170272465</v>
       </c>
       <c r="F68">
-        <v>-2.360117453544232</v>
+        <v>-2.870396743873145</v>
       </c>
       <c r="G68">
-        <v>-1.609075257303398</v>
+        <v>-1.982617352681523</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.910607975970137</v>
       </c>
       <c r="E69">
-        <v>-8.136048674796488</v>
+        <v>-10.35669911630784</v>
       </c>
       <c r="F69">
-        <v>-2.386830645549711</v>
+        <v>-2.622216213259607</v>
       </c>
       <c r="G69">
-        <v>-1.052271292507838</v>
+        <v>-2.548723950442435</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.685807703699203</v>
       </c>
       <c r="E70">
-        <v>-8.263824097396915</v>
+        <v>-10.41740783885467</v>
       </c>
       <c r="F70">
-        <v>-2.309736976473369</v>
+        <v>-2.797521949979261</v>
       </c>
       <c r="G70">
-        <v>-1.860835624473893</v>
+        <v>-2.977538914144232</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.454946714750053</v>
       </c>
       <c r="E71">
-        <v>-8.791576986724825</v>
+        <v>-10.05686885225998</v>
       </c>
       <c r="F71">
-        <v>-2.5232362490339</v>
+        <v>-2.835278936198863</v>
       </c>
       <c r="G71">
-        <v>-1.446120274223852</v>
+        <v>-2.58463343790691</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.230901499466448</v>
       </c>
       <c r="E72">
-        <v>-9.071939341013707</v>
+        <v>-9.292335642493015</v>
       </c>
       <c r="F72">
-        <v>-2.303742909946712</v>
+        <v>-2.798617051685762</v>
       </c>
       <c r="G72">
-        <v>-1.602318433857746</v>
+        <v>-3.270700963828853</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.028360611772447</v>
       </c>
       <c r="E73">
-        <v>-8.94307255617743</v>
+        <v>-10.45855355368836</v>
       </c>
       <c r="F73">
-        <v>-2.326273674935456</v>
+        <v>-3.279201027359118</v>
       </c>
       <c r="G73">
-        <v>-0.7358592815009155</v>
+        <v>-2.898837315039138</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.856813502943718</v>
       </c>
       <c r="E74">
-        <v>-8.786568494472343</v>
+        <v>-11.09351353667386</v>
       </c>
       <c r="F74">
-        <v>-2.68951609453265</v>
+        <v>-3.031101676751054</v>
       </c>
       <c r="G74">
-        <v>-1.401212723983639</v>
+        <v>-2.753342149133709</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.723734547045831</v>
       </c>
       <c r="E75">
-        <v>-8.786083947753522</v>
+        <v>-10.26682702115161</v>
       </c>
       <c r="F75">
-        <v>-2.588108185449338</v>
+        <v>-3.097308941419805</v>
       </c>
       <c r="G75">
-        <v>-1.522358827447729</v>
+        <v>-2.949210575964689</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.634143921694084</v>
       </c>
       <c r="E76">
-        <v>-8.648771558892941</v>
+        <v>-11.60350575094369</v>
       </c>
       <c r="F76">
-        <v>-2.986416225574438</v>
+        <v>-2.945972015500155</v>
       </c>
       <c r="G76">
-        <v>-0.900691343901228</v>
+        <v>-2.79912368339629</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.587001072058772</v>
       </c>
       <c r="E77">
-        <v>-8.09191869559174</v>
+        <v>-11.49664734978469</v>
       </c>
       <c r="F77">
-        <v>-2.497961102839681</v>
+        <v>-2.965951408888276</v>
       </c>
       <c r="G77">
-        <v>-0.8024806999332089</v>
+        <v>-2.614534285217607</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.578525147577657</v>
       </c>
       <c r="E78">
-        <v>-9.561589650041078</v>
+        <v>-11.49767531338443</v>
       </c>
       <c r="F78">
-        <v>-2.925853456388363</v>
+        <v>-3.11055205108836</v>
       </c>
       <c r="G78">
-        <v>-0.9111526678053249</v>
+        <v>-2.152464891573831</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.604214817148072</v>
       </c>
       <c r="E79">
-        <v>-10.55945701152727</v>
+        <v>-12.2473279575622</v>
       </c>
       <c r="F79">
-        <v>-3.111751527087614</v>
+        <v>-3.2381844154095</v>
       </c>
       <c r="G79">
-        <v>-0.8831322103609336</v>
+        <v>-2.482595803295494</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.658719725115714</v>
       </c>
       <c r="E80">
-        <v>-11.16911641023192</v>
+        <v>-12.56523588984867</v>
       </c>
       <c r="F80">
-        <v>-3.008279326436525</v>
+        <v>-3.372480995486161</v>
       </c>
       <c r="G80">
-        <v>-1.697215221740954</v>
+        <v>-2.091878597659629</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.736225151918672</v>
       </c>
       <c r="E81">
-        <v>-11.0753543559031</v>
+        <v>-12.94984371579412</v>
       </c>
       <c r="F81">
-        <v>-3.213706158656775</v>
+        <v>-3.250757375849191</v>
       </c>
       <c r="G81">
-        <v>-0.3188695864653954</v>
+        <v>-1.846534067744242</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.834519820035539</v>
       </c>
       <c r="E82">
-        <v>-12.18184622341129</v>
+        <v>-14.09322453256879</v>
       </c>
       <c r="F82">
-        <v>-3.226419113187538</v>
+        <v>-3.626584353029715</v>
       </c>
       <c r="G82">
-        <v>-0.8299052591805315</v>
+        <v>-2.499102183354299</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.954398075427874</v>
       </c>
       <c r="E83">
-        <v>-14.16736470902237</v>
+        <v>-15.02193756748385</v>
       </c>
       <c r="F83">
-        <v>-3.765001232567902</v>
+        <v>-3.362125574583765</v>
       </c>
       <c r="G83">
-        <v>-0.5180187639257929</v>
+        <v>-1.990969859077104</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.096101722952812</v>
       </c>
       <c r="E84">
-        <v>-11.88029513924052</v>
+        <v>-15.89051699605105</v>
       </c>
       <c r="F84">
-        <v>-3.71313300764161</v>
+        <v>-3.614906029385048</v>
       </c>
       <c r="G84">
-        <v>0.3060654055283659</v>
+        <v>-2.221565908615039</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.26269846334812</v>
       </c>
       <c r="E85">
-        <v>-14.60653611828624</v>
+        <v>-16.79766543774159</v>
       </c>
       <c r="F85">
-        <v>-3.866263348988321</v>
+        <v>-3.593006480357237</v>
       </c>
       <c r="G85">
-        <v>-0.4438029540264115</v>
+        <v>-1.896387573020127</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.461375072663563</v>
       </c>
       <c r="E86">
-        <v>-16.09464701889481</v>
+        <v>-17.51065102787925</v>
       </c>
       <c r="F86">
-        <v>-4.026081928745236</v>
+        <v>-4.007642470358919</v>
       </c>
       <c r="G86">
-        <v>0.1736799999584504</v>
+        <v>-1.215583814505625</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.695393820070144</v>
       </c>
       <c r="E87">
-        <v>-17.49550328232359</v>
+        <v>-19.04774643182879</v>
       </c>
       <c r="F87">
-        <v>-4.260830481922379</v>
+        <v>-3.862433806485179</v>
       </c>
       <c r="G87">
-        <v>1.200571499693901</v>
+        <v>-1.747644761940672</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.967201378126195</v>
       </c>
       <c r="E88">
-        <v>-18.06659819637892</v>
+        <v>-20.11699160062388</v>
       </c>
       <c r="F88">
-        <v>-4.204223995452075</v>
+        <v>-3.879045058013518</v>
       </c>
       <c r="G88">
-        <v>-0.4876312664208227</v>
+        <v>-1.784024346871723</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.282201035127272</v>
       </c>
       <c r="E89">
-        <v>-19.5181144985315</v>
+        <v>-21.76252131468709</v>
       </c>
       <c r="F89">
-        <v>-4.045960261310215</v>
+        <v>-4.160719796191851</v>
       </c>
       <c r="G89">
-        <v>-0.2212680828766022</v>
+        <v>-2.013736480750672</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.636583999151203</v>
       </c>
       <c r="E90">
-        <v>-22.01083112994968</v>
+        <v>-23.30078959340462</v>
       </c>
       <c r="F90">
-        <v>-4.418800145636245</v>
+        <v>-4.304564138953179</v>
       </c>
       <c r="G90">
-        <v>-0.9162045602982527</v>
+        <v>-1.67306810257751</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.023139650466028</v>
       </c>
       <c r="E91">
-        <v>-24.210800030668</v>
+        <v>-25.49512960093141</v>
       </c>
       <c r="F91">
-        <v>-4.210556035879074</v>
+        <v>-4.117865036975421</v>
       </c>
       <c r="G91">
-        <v>0.379519789953715</v>
+        <v>-1.792049109258917</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.438751772562274</v>
       </c>
       <c r="E92">
-        <v>-24.41075027200268</v>
+        <v>-26.88035810055971</v>
       </c>
       <c r="F92">
-        <v>-4.179232150909614</v>
+        <v>-4.35419825699412</v>
       </c>
       <c r="G92">
-        <v>-0.8893361727015278</v>
+        <v>-1.864265349652578</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.871454837040936</v>
       </c>
       <c r="E93">
-        <v>-26.61308756462701</v>
+        <v>-28.72840570071995</v>
       </c>
       <c r="F93">
-        <v>-4.82781814791214</v>
+        <v>-4.648566068885549</v>
       </c>
       <c r="G93">
-        <v>-0.3229581102063953</v>
+        <v>-2.604066340222432</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.30714638686503</v>
       </c>
       <c r="E94">
-        <v>-29.18950398112896</v>
+        <v>-31.30637311956953</v>
       </c>
       <c r="F94">
-        <v>-4.944544227008021</v>
+        <v>-4.791563820161217</v>
       </c>
       <c r="G94">
-        <v>-0.6106577597512185</v>
+        <v>-1.761423252475119</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.73885288880075</v>
       </c>
       <c r="E95">
-        <v>-31.6022002125946</v>
+        <v>-34.11637954657213</v>
       </c>
       <c r="F95">
-        <v>-4.883269061855539</v>
+        <v>-4.677633481049784</v>
       </c>
       <c r="G95">
-        <v>-0.1445230161852176</v>
+        <v>-2.54847565952699</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.15083824506175</v>
       </c>
       <c r="E96">
-        <v>-34.49977826995754</v>
+        <v>-35.3900581459695</v>
       </c>
       <c r="F96">
-        <v>-5.649523820058332</v>
+        <v>-4.95430570848261</v>
       </c>
       <c r="G96">
-        <v>-0.8743923701372577</v>
+        <v>-2.292656563525348</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.5262449918006</v>
       </c>
       <c r="E97">
-        <v>-36.28204525668235</v>
+        <v>-37.9052178945697</v>
       </c>
       <c r="F97">
-        <v>-4.948343948284663</v>
+        <v>-5.271500012525583</v>
       </c>
       <c r="G97">
-        <v>-1.137610535419171</v>
+        <v>-2.690670211529766</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.85965357187661</v>
       </c>
       <c r="E98">
-        <v>-39.8411586467448</v>
+        <v>-40.46429478409627</v>
       </c>
       <c r="F98">
-        <v>-5.845030952630057</v>
+        <v>-5.605728035472322</v>
       </c>
       <c r="G98">
-        <v>-1.290716645519384</v>
+        <v>-2.663268826101219</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.13621186019196</v>
       </c>
       <c r="E99">
-        <v>-41.84583257740833</v>
+        <v>-43.22886476714292</v>
       </c>
       <c r="F99">
-        <v>-6.322496953399275</v>
+        <v>-5.365766566229361</v>
       </c>
       <c r="G99">
-        <v>-2.022267756605374</v>
+        <v>-3.274852387935099</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.35267980620799</v>
       </c>
       <c r="E100">
-        <v>-45.20819962149653</v>
+        <v>-45.07635536500021</v>
       </c>
       <c r="F100">
-        <v>-6.019693047877736</v>
+        <v>-5.739802613085033</v>
       </c>
       <c r="G100">
-        <v>-2.040181118518371</v>
+        <v>-3.066145665502825</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.50729993862389</v>
       </c>
       <c r="E101">
-        <v>-46.64810944476746</v>
+        <v>-47.38365815664833</v>
       </c>
       <c r="F101">
-        <v>-6.371258386381367</v>
+        <v>-6.0086749330531</v>
       </c>
       <c r="G101">
-        <v>-2.798812492115599</v>
+        <v>-3.233387805055727</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.61056378457438</v>
       </c>
       <c r="E102">
-        <v>-50.06732581942945</v>
+        <v>-49.87406979479661</v>
       </c>
       <c r="F102">
-        <v>-6.227078969005606</v>
+        <v>-5.81897796944461</v>
       </c>
       <c r="G102">
-        <v>-2.77027890011262</v>
+        <v>-3.627236786771742</v>
       </c>
     </row>
   </sheetData>
